--- a/data/base/Backlog_13.xlsx
+++ b/data/base/Backlog_13.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B517CA5D-4935-4D7C-AE56-C83ADAF57C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FCFB80-32CC-467A-890B-6FA01857117B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -943,7 +943,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
   <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="48.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="11" bestFit="1" customWidth="1"/>
@@ -952,11 +952,11 @@
     <col min="5" max="5" width="21.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="11"/>
+    <col min="8" max="8" width="8.85546875" style="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.28515625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="11"/>
+    <col min="12" max="16384" width="48.28515625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1017,7 +1017,7 @@
         <v>9411</v>
       </c>
       <c r="H2" s="13">
-        <v>46045.666400462964</v>
+        <v>46023</v>
       </c>
       <c r="I2" s="7">
         <v>46118</v>
@@ -1052,7 +1052,7 @@
         <v>13386</v>
       </c>
       <c r="H3" s="13">
-        <v>46105.601006944446</v>
+        <v>46082</v>
       </c>
       <c r="I3" s="7">
         <v>46118</v>
@@ -1087,7 +1087,7 @@
         <v>13435</v>
       </c>
       <c r="H4" s="13">
-        <v>46105.607372685183</v>
+        <v>46082</v>
       </c>
       <c r="I4" s="7">
         <v>46118</v>
@@ -1122,7 +1122,7 @@
         <v>13446</v>
       </c>
       <c r="H5" s="13">
-        <v>46105.680798611109</v>
+        <v>46082</v>
       </c>
       <c r="I5" s="7">
         <v>46118</v>
@@ -1157,7 +1157,7 @@
         <v>13764</v>
       </c>
       <c r="H6" s="13">
-        <v>46112.414629629631</v>
+        <v>46082</v>
       </c>
       <c r="I6" s="7">
         <v>46118</v>
@@ -1192,7 +1192,7 @@
         <v>13800</v>
       </c>
       <c r="H7" s="13">
-        <v>46108.708333333336</v>
+        <v>46082</v>
       </c>
       <c r="I7" s="7">
         <v>46118</v>
@@ -1227,7 +1227,7 @@
         <v>13829</v>
       </c>
       <c r="H8" s="13">
-        <v>46113.447395833333</v>
+        <v>46113</v>
       </c>
       <c r="I8" s="7">
         <v>46118</v>
@@ -1262,7 +1262,7 @@
         <v>13876</v>
       </c>
       <c r="H9" s="13">
-        <v>46112.694756944446</v>
+        <v>46082</v>
       </c>
       <c r="I9" s="7">
         <v>46118</v>
@@ -1297,7 +1297,7 @@
         <v>14007</v>
       </c>
       <c r="H10" s="13">
-        <v>46114.429525462961</v>
+        <v>46113</v>
       </c>
       <c r="I10" s="7">
         <v>46118</v>
@@ -1332,7 +1332,7 @@
         <v>14016</v>
       </c>
       <c r="H11" s="13">
-        <v>46114.356689814813</v>
+        <v>46113</v>
       </c>
       <c r="I11" s="7">
         <v>46118</v>
@@ -1367,7 +1367,7 @@
         <v>14030</v>
       </c>
       <c r="H12" s="13">
-        <v>46113.568472222221</v>
+        <v>46113</v>
       </c>
       <c r="I12" s="7">
         <v>46118</v>
@@ -1402,7 +1402,7 @@
         <v>14068</v>
       </c>
       <c r="H13" s="13">
-        <v>46115.560995370368</v>
+        <v>46113</v>
       </c>
       <c r="I13" s="7">
         <v>46118</v>
@@ -1437,7 +1437,7 @@
         <v>14091</v>
       </c>
       <c r="H14" s="13">
-        <v>46115.662233796298</v>
+        <v>46113</v>
       </c>
       <c r="I14" s="7">
         <v>46118</v>
@@ -1472,7 +1472,7 @@
         <v>14098</v>
       </c>
       <c r="H15" s="13">
-        <v>46115.438043981485</v>
+        <v>46113</v>
       </c>
       <c r="I15" s="7">
         <v>46118</v>
@@ -1507,7 +1507,7 @@
         <v>14130</v>
       </c>
       <c r="H16" s="13">
-        <v>46115.640659722223</v>
+        <v>46113</v>
       </c>
       <c r="I16" s="7">
         <v>46118</v>
@@ -1542,7 +1542,7 @@
         <v>14136</v>
       </c>
       <c r="H17" s="13">
-        <v>46118.565335648149</v>
+        <v>46113</v>
       </c>
       <c r="I17" s="7">
         <v>46118</v>
@@ -1577,7 +1577,7 @@
         <v>14145</v>
       </c>
       <c r="H18" s="13">
-        <v>46115.583333333336</v>
+        <v>46113</v>
       </c>
       <c r="I18" s="7">
         <v>46118</v>
@@ -1612,7 +1612,7 @@
         <v>14204</v>
       </c>
       <c r="H19" s="13">
-        <v>46118.492581018516</v>
+        <v>46113</v>
       </c>
       <c r="I19" s="7">
         <v>46118</v>
@@ -1647,7 +1647,7 @@
         <v>14217</v>
       </c>
       <c r="H20" s="13">
-        <v>46118.70175925926</v>
+        <v>46113</v>
       </c>
       <c r="I20" s="7">
         <v>46118</v>
@@ -1682,7 +1682,7 @@
         <v>14220</v>
       </c>
       <c r="H21" s="13">
-        <v>46119.417222222219</v>
+        <v>46113</v>
       </c>
       <c r="I21" s="7">
         <v>46118</v>
@@ -1717,7 +1717,7 @@
         <v>14297</v>
       </c>
       <c r="H22" s="13">
-        <v>46118.333379629628</v>
+        <v>46113</v>
       </c>
       <c r="I22" s="7">
         <v>46118</v>
@@ -1752,7 +1752,7 @@
         <v>14425</v>
       </c>
       <c r="H23" s="13">
-        <v>46119.416666666664</v>
+        <v>46113</v>
       </c>
       <c r="I23" s="7">
         <v>46118</v>

--- a/data/base/Backlog_13.xlsx
+++ b/data/base/Backlog_13.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FCFB80-32CC-467A-890B-6FA01857117B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EFF2F3A-04FE-4212-8154-3DEE306F9BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="32">
   <si>
     <t>Status</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>Emerson Pellis</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -689,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6">
         <v>2026</v>
@@ -704,7 +707,7 @@
         <v>46122</v>
       </c>
       <c r="G3" s="6">
-        <v>13326</v>
+        <v>13383</v>
       </c>
       <c r="H3" s="13">
         <v>46082</v>
@@ -724,7 +727,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="6">
         <v>2026</v>
@@ -739,10 +742,10 @@
         <v>46122</v>
       </c>
       <c r="G4" s="6">
-        <v>13348</v>
+        <v>14120</v>
       </c>
       <c r="H4" s="13">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="I4" s="7">
         <v>46118</v>
@@ -759,7 +762,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" s="6">
         <v>2026</v>
@@ -774,7 +777,7 @@
         <v>46122</v>
       </c>
       <c r="G5" s="6">
-        <v>13383</v>
+        <v>13326</v>
       </c>
       <c r="H5" s="13">
         <v>46082</v>
@@ -794,7 +797,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C6" s="6">
         <v>2026</v>
@@ -809,7 +812,7 @@
         <v>46122</v>
       </c>
       <c r="G6" s="6">
-        <v>13451</v>
+        <v>13348</v>
       </c>
       <c r="H6" s="13">
         <v>46082</v>
@@ -853,7 +856,7 @@
         <v>46118</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>14</v>
@@ -864,7 +867,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="6">
         <v>2026</v>
@@ -879,7 +882,7 @@
         <v>46122</v>
       </c>
       <c r="G8" s="6">
-        <v>14120</v>
+        <v>14131</v>
       </c>
       <c r="H8" s="13">
         <v>46113</v>
@@ -899,7 +902,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" s="6">
         <v>2026</v>
@@ -914,16 +917,16 @@
         <v>46122</v>
       </c>
       <c r="G9" s="6">
-        <v>14131</v>
+        <v>13451</v>
       </c>
       <c r="H9" s="13">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="I9" s="7">
         <v>46118</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>14</v>
@@ -931,7 +934,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H22">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H9">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
@@ -943,7 +946,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
   <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultColWidth="48.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="11" bestFit="1" customWidth="1"/>
@@ -952,11 +955,11 @@
     <col min="5" max="5" width="21.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="11"/>
     <col min="9" max="9" width="11.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.28515625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="48.28515625" style="11"/>
+    <col min="12" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -999,7 +1002,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1">
         <v>2026</v>
@@ -1014,16 +1017,16 @@
         <v>46122</v>
       </c>
       <c r="G2" s="6">
-        <v>9411</v>
+        <v>14220</v>
       </c>
       <c r="H2" s="13">
-        <v>46023</v>
+        <v>46045.666400462964</v>
       </c>
       <c r="I2" s="7">
         <v>46118</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>1</v>
@@ -1034,7 +1037,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
         <v>2026</v>
@@ -1049,10 +1052,10 @@
         <v>46122</v>
       </c>
       <c r="G3" s="6">
-        <v>13386</v>
+        <v>9411</v>
       </c>
       <c r="H3" s="13">
-        <v>46082</v>
+        <v>46105.601006944446</v>
       </c>
       <c r="I3" s="7">
         <v>46118</v>
@@ -1069,7 +1072,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
         <v>2026</v>
@@ -1084,10 +1087,10 @@
         <v>46122</v>
       </c>
       <c r="G4" s="6">
-        <v>13435</v>
+        <v>14091</v>
       </c>
       <c r="H4" s="13">
-        <v>46082</v>
+        <v>46105.607372685183</v>
       </c>
       <c r="I4" s="7">
         <v>46118</v>
@@ -1119,10 +1122,10 @@
         <v>46122</v>
       </c>
       <c r="G5" s="6">
-        <v>13446</v>
+        <v>13435</v>
       </c>
       <c r="H5" s="13">
-        <v>46082</v>
+        <v>46105.680798611109</v>
       </c>
       <c r="I5" s="7">
         <v>46118</v>
@@ -1139,7 +1142,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1">
         <v>2026</v>
@@ -1154,10 +1157,10 @@
         <v>46122</v>
       </c>
       <c r="G6" s="6">
-        <v>13764</v>
+        <v>13446</v>
       </c>
       <c r="H6" s="13">
-        <v>46082</v>
+        <v>46112.414629629631</v>
       </c>
       <c r="I6" s="7">
         <v>46118</v>
@@ -1174,7 +1177,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1">
         <v>2026</v>
@@ -1189,10 +1192,10 @@
         <v>46122</v>
       </c>
       <c r="G7" s="6">
-        <v>13800</v>
+        <v>13829</v>
       </c>
       <c r="H7" s="13">
-        <v>46082</v>
+        <v>46108.708333333336</v>
       </c>
       <c r="I7" s="7">
         <v>46118</v>
@@ -1224,10 +1227,10 @@
         <v>46122</v>
       </c>
       <c r="G8" s="6">
-        <v>13829</v>
+        <v>13876</v>
       </c>
       <c r="H8" s="13">
-        <v>46113</v>
+        <v>46113.447395833333</v>
       </c>
       <c r="I8" s="7">
         <v>46118</v>
@@ -1259,16 +1262,16 @@
         <v>46122</v>
       </c>
       <c r="G9" s="6">
-        <v>13876</v>
+        <v>14016</v>
       </c>
       <c r="H9" s="13">
-        <v>46082</v>
+        <v>46112.694756944446</v>
       </c>
       <c r="I9" s="7">
         <v>46118</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>1</v>
@@ -1279,7 +1282,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1">
         <v>2026</v>
@@ -1294,10 +1297,10 @@
         <v>46122</v>
       </c>
       <c r="G10" s="6">
-        <v>14007</v>
+        <v>14098</v>
       </c>
       <c r="H10" s="13">
-        <v>46113</v>
+        <v>46114.429525462961</v>
       </c>
       <c r="I10" s="7">
         <v>46118</v>
@@ -1329,10 +1332,10 @@
         <v>46122</v>
       </c>
       <c r="G11" s="6">
-        <v>14016</v>
+        <v>14130</v>
       </c>
       <c r="H11" s="13">
-        <v>46113</v>
+        <v>46114.356689814813</v>
       </c>
       <c r="I11" s="7">
         <v>46118</v>
@@ -1349,7 +1352,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1">
         <v>2026</v>
@@ -1364,10 +1367,10 @@
         <v>46122</v>
       </c>
       <c r="G12" s="6">
-        <v>14030</v>
+        <v>14145</v>
       </c>
       <c r="H12" s="13">
-        <v>46113</v>
+        <v>46113.568472222221</v>
       </c>
       <c r="I12" s="7">
         <v>46118</v>
@@ -1384,7 +1387,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1">
         <v>2026</v>
@@ -1399,16 +1402,16 @@
         <v>46122</v>
       </c>
       <c r="G13" s="6">
-        <v>14068</v>
+        <v>14217</v>
       </c>
       <c r="H13" s="13">
-        <v>46113</v>
+        <v>46115.560995370368</v>
       </c>
       <c r="I13" s="7">
         <v>46118</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>1</v>
@@ -1419,7 +1422,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1">
         <v>2026</v>
@@ -1434,10 +1437,10 @@
         <v>46122</v>
       </c>
       <c r="G14" s="6">
-        <v>14091</v>
+        <v>14007</v>
       </c>
       <c r="H14" s="13">
-        <v>46113</v>
+        <v>46115.662233796298</v>
       </c>
       <c r="I14" s="7">
         <v>46118</v>
@@ -1454,7 +1457,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1">
         <v>2026</v>
@@ -1469,10 +1472,10 @@
         <v>46122</v>
       </c>
       <c r="G15" s="6">
-        <v>14098</v>
+        <v>14204</v>
       </c>
       <c r="H15" s="13">
-        <v>46113</v>
+        <v>46115.438043981485</v>
       </c>
       <c r="I15" s="7">
         <v>46118</v>
@@ -1489,7 +1492,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1">
         <v>2026</v>
@@ -1504,10 +1507,10 @@
         <v>46122</v>
       </c>
       <c r="G16" s="6">
-        <v>14130</v>
+        <v>13386</v>
       </c>
       <c r="H16" s="13">
-        <v>46113</v>
+        <v>46115.640659722223</v>
       </c>
       <c r="I16" s="7">
         <v>46118</v>
@@ -1542,7 +1545,7 @@
         <v>14136</v>
       </c>
       <c r="H17" s="13">
-        <v>46113</v>
+        <v>46118.565335648149</v>
       </c>
       <c r="I17" s="7">
         <v>46118</v>
@@ -1559,7 +1562,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C18" s="1">
         <v>2026</v>
@@ -1574,16 +1577,16 @@
         <v>46122</v>
       </c>
       <c r="G18" s="6">
-        <v>14145</v>
+        <v>14425</v>
       </c>
       <c r="H18" s="13">
-        <v>46113</v>
+        <v>46115.583333333336</v>
       </c>
       <c r="I18" s="7">
         <v>46118</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>1</v>
@@ -1594,7 +1597,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C19" s="1">
         <v>2026</v>
@@ -1609,16 +1612,16 @@
         <v>46122</v>
       </c>
       <c r="G19" s="6">
-        <v>14204</v>
+        <v>13764</v>
       </c>
       <c r="H19" s="13">
-        <v>46113</v>
+        <v>46118.492581018516</v>
       </c>
       <c r="I19" s="7">
         <v>46118</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>1</v>
@@ -1629,7 +1632,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C20" s="1">
         <v>2026</v>
@@ -1644,16 +1647,16 @@
         <v>46122</v>
       </c>
       <c r="G20" s="6">
-        <v>14217</v>
+        <v>13800</v>
       </c>
       <c r="H20" s="13">
-        <v>46113</v>
+        <v>46118.70175925926</v>
       </c>
       <c r="I20" s="7">
         <v>46118</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>1</v>
@@ -1664,7 +1667,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C21" s="1">
         <v>2026</v>
@@ -1679,16 +1682,16 @@
         <v>46122</v>
       </c>
       <c r="G21" s="6">
-        <v>14220</v>
+        <v>14068</v>
       </c>
       <c r="H21" s="13">
-        <v>46113</v>
+        <v>46119.417222222219</v>
       </c>
       <c r="I21" s="7">
         <v>46118</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>1</v>
@@ -1714,10 +1717,10 @@
         <v>46122</v>
       </c>
       <c r="G22" s="6">
-        <v>14297</v>
+        <v>14030</v>
       </c>
       <c r="H22" s="13">
-        <v>46113</v>
+        <v>46118.333379629628</v>
       </c>
       <c r="I22" s="7">
         <v>46118</v>
@@ -1734,7 +1737,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="1">
         <v>2026</v>
@@ -1749,16 +1752,16 @@
         <v>46122</v>
       </c>
       <c r="G23" s="6">
-        <v>14425</v>
+        <v>14297</v>
       </c>
       <c r="H23" s="13">
-        <v>46113</v>
+        <v>46119.416666666664</v>
       </c>
       <c r="I23" s="7">
         <v>46118</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>1</v>
@@ -1766,7 +1769,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G24">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G23">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
